--- a/checklist_forms/032_spring_deep_cleaning_checklist--checklist_forms.xlsx
+++ b/checklist_forms/032_spring_deep_cleaning_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spring_deep_cleaning_tasks</t>
+          <t>Task List</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>spring_deep_cleaning_notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spring_deep_cleaning_notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>seasonal_notes</t>
+          <t>Seasonal Notes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>completed_tasks</t>
+          <t>Completed Tasks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>completed_tasks</t>
+          <t>seasonal_refresh_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>completed_tasks</t>
+          <t>Refresh Date (YYYY-MM-LL)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>seasonal_refresh_date</t>
+          <t>spring_cleaning_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>seasonal_refresh_date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>YYYY-MM-LL</t>
-        </is>
-      </c>
+          <t>Select a cleaning frequency</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency</t>
+          <t>seasonal_cleaning_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency</t>
+          <t>Seasonal Cleaning Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>seasonal_frequency_notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Seasonal Frequency Notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency_frequency</t>
+          <t>spring_cleaning_frequency_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency_frequency</t>
+          <t>Spring Cleaning Frequency Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>seasonal_cleaning_frequency</t>
+          <t>seasonal_refresh_frequency</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seasonal_cleaning_frequency</t>
+          <t>Refresh Frequency</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -800,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency_notes</t>
+          <t>seasonal_frequency</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>spring_cleaning_frequency_notes</t>
+          <t>Seasonal Frequency</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>seasonal_notes</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>seasonal_notes</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>seasonal_cleaning_frequency_notes</t>
+          <t>Seasonal Cleaning Frequency Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>seasonal_frequency</t>
+          <t>seasonal_refresh_notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>seasonal_frequency</t>
+          <t>Refresh Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>seasonal_cleaning_frequency</t>
+          <t>seasonal_frequency_refresh_notes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>seasonal_cleaning_frequency</t>
+          <t>Seasonal Frequency Refresh Notes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>seasonal_frequency</t>
+          <t>seasonal_frequency_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>seasonal_frequency</t>
+          <t>Seasonal Frequency 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>seasonal_frequency_notes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>seasonal_notes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>seasonal_notes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>seasonal_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>seasonal_refresh_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>seasonal_refresh_frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>seasonal_frequency_notes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>seasonal_frequency_notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>seasonal_frequency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1237,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bi-annually</t>
+          <t>bi-annual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bi-Annually</t>
+          <t>Bi-Annual</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
